--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104576_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104576_W14.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.019500000000001</v>
+        <v>8.3858</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5358</v>
+        <v>6.5715</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4837</v>
+        <v>1.8144</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8538</v>
+        <v>7.9178</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6192</v>
+        <v>2.1653</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2346</v>
+        <v>5.7524</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8291</v>
+        <v>7.8841</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0855</v>
+        <v>1.7926</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7436</v>
+        <v>6.0915</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0247</v>
+        <v>0.0336</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5337</v>
+        <v>0.3727</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.3391</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7781</v>
+        <v>-0.2148</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5194</v>
+        <v>-0.1745</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2587</v>
+        <v>-0.0403</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.3941</v>
+        <v>5.5521</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0161</v>
+        <v>3.7264</v>
       </c>
       <c r="F3" t="n">
-        <v>1.378</v>
+        <v>1.8257</v>
       </c>
       <c r="G3" t="n">
-        <v>7.9243</v>
+        <v>3.8426</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1615</v>
+        <v>3.6025</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7628</v>
+        <v>0.2401</v>
       </c>
       <c r="J3" t="n">
-        <v>7.9155</v>
+        <v>3.7945</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8009</v>
+        <v>3.0574</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1145</v>
+        <v>0.7371</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0481</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3605</v>
+        <v>0.5451</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3517</v>
+        <v>-0.497</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2107</v>
+        <v>1.3241</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7652</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4455</v>
+        <v>0.5696</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9779</v>
+        <v>4.2571</v>
       </c>
       <c r="E4" t="n">
-        <v>4.074</v>
+        <v>3.018</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0961</v>
+        <v>1.2391</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9448</v>
+        <v>1.8471</v>
       </c>
       <c r="H4" t="n">
-        <v>1.772</v>
+        <v>-0.2446</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1728</v>
+        <v>2.0916</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0528</v>
+        <v>1.9148</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7419</v>
+        <v>-0.6173</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3109</v>
+        <v>2.5321</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.108</v>
+        <v>-0.0678</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0301</v>
+        <v>0.3727</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1381</v>
+        <v>-0.4405</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.245</v>
+        <v>-0.0452</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0212</v>
+        <v>0.2413</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2238</v>
+        <v>-0.2865</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5045</v>
+        <v>3.7524</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3214</v>
+        <v>3.814</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1831</v>
+        <v>-0.0616</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8345</v>
+        <v>2.9417</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2526</v>
+        <v>1.7693</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0871</v>
+        <v>1.1723</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9243</v>
+        <v>4.028</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6132</v>
+        <v>1.7269</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5375</v>
+        <v>2.301</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0898</v>
+        <v>-1.0863</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3605</v>
+        <v>0.0424</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4504</v>
+        <v>-1.1287</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7836</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4688</v>
+        <v>-0.214</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3149</v>
+        <v>0.2232</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5799</v>
+        <v>1.9433</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4832</v>
+        <v>1.6893</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.2541</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5245</v>
+        <v>1.5184</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5036</v>
+        <v>0.5027</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0209</v>
+        <v>1.0157</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3179</v>
+        <v>2.2888</v>
       </c>
       <c r="K6" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L6" t="n">
-        <v>2.159</v>
+        <v>2.1444</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7935</v>
+        <v>-0.7704</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8934</v>
+        <v>-0.5342</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6079</v>
+        <v>-0.3719</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2855</v>
+        <v>-0.1623</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.455</v>
+        <v>1.3328</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1451</v>
+        <v>0.9712</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3098</v>
+        <v>0.3616</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5067</v>
+        <v>0.5202</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1384</v>
+        <v>1.1456</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6317</v>
+        <v>-0.6254</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6634</v>
+        <v>0.6605</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1567</v>
+        <v>-0.1403</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1878</v>
+        <v>-0.324</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3871</v>
+        <v>0.2228</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.575</v>
+        <v>-0.5468</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8969</v>
+        <v>1.2612</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1132</v>
+        <v>1.3134</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2164</v>
+        <v>-0.0522</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4311</v>
+        <v>-1.0258</v>
       </c>
       <c r="H8" t="n">
-        <v>0.44</v>
+        <v>0.5278</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8711</v>
+        <v>-1.5537</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1914</v>
+        <v>0.4749</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0795</v>
+        <v>0.1551</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>0.3198</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6225</v>
+        <v>-1.5007</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9831</v>
+        <v>-1.8734</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0746</v>
+        <v>-0.3472</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0294</v>
+        <v>-0.2023</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9548</v>
+        <v>-0.1449</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2534</v>
+        <v>2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2534</v>
+        <v>2.1789</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8637</v>
+        <v>-0.1048</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9114</v>
+        <v>0.8711</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0477</v>
+        <v>-0.9759</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0376</v>
+        <v>-1.4183</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5164</v>
+        <v>0.4449</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.554</v>
+        <v>-1.8632</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4863</v>
+        <v>0.1839</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1559</v>
+        <v>0.0722</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3304</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5239</v>
+        <v>-1.6022</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8844</v>
+        <v>-1.9749</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7377</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6261</v>
+        <v>0.8057</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1116</v>
+        <v>-0.7396</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1853</v>
+        <v>1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1853</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0639</v>
+        <v>-0.2991</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1433</v>
+        <v>1.8785</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2072</v>
+        <v>-2.1776</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0178</v>
+        <v>-0.025</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8614</v>
+        <v>1.8611</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8793</v>
+        <v>-1.8862</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4879</v>
+        <v>0.4572</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6825</v>
+        <v>-0.7009</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5057</v>
+        <v>-0.4822</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9799</v>
+        <v>-0.2042</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3297</v>
+        <v>0.4504</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6503</v>
+        <v>-0.6546</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1607</v>
+        <v>-1.4001</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7067</v>
+        <v>-0.8435</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4539</v>
+        <v>-0.5566</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5964</v>
+        <v>1.595</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0447</v>
+        <v>1.0454</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5517</v>
+        <v>0.5496</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0436</v>
+        <v>2.0207</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3753</v>
+        <v>1.3624</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4471</v>
+        <v>-0.4257</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3764</v>
+        <v>0.3871</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4888</v>
+        <v>0.2812</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>0.5503</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.141</v>
+        <v>-0.2691</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9772</v>
+        <v>-2.9859</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8309</v>
+        <v>-2.8412</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1463</v>
+        <v>-0.1447</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1595</v>
+        <v>-1.162</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2743</v>
+        <v>-3.1194</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6296</v>
+        <v>-0.5178</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6447</v>
+        <v>-2.6015</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9076</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1746</v>
+        <v>0.1752</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0822</v>
+        <v>-1.0799</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5716</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4817</v>
+        <v>-1.4763</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.206</v>
+        <v>-0.0569</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.2154</v>
+        <v>18.57540000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>19.5763</v>
+        <v>19.6509</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.361</v>
+        <v>-1.075199999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>15.6314</v>
+        <v>15.647</v>
       </c>
       <c r="H14" t="n">
-        <v>12.1928</v>
+        <v>12.2056</v>
       </c>
       <c r="I14" t="n">
-        <v>3.438400000000001</v>
+        <v>3.440899999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>23.6999</v>
+        <v>23.4894</v>
       </c>
       <c r="K14" t="n">
-        <v>8.587300000000001</v>
+        <v>8.4785</v>
       </c>
       <c r="L14" t="n">
-        <v>15.1126</v>
+        <v>15.0108</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.0686</v>
+        <v>-7.8426</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6052</v>
+        <v>3.727</v>
       </c>
       <c r="O14" t="n">
-        <v>-11.6741</v>
+        <v>-11.5697</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4026</v>
+        <v>3.414600000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R14" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5293000000000004</v>
+        <v>-0.1851000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6029</v>
+        <v>1.9716</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.1325</v>
+        <v>-2.157</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2891000000000005</v>
+        <v>-0.3005000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>6.749099999999999</v>
+        <v>6.7094</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.038100000000001</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1537</v>
+        <v>4.1698</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8232</v>
+        <v>2.6215</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3305</v>
+        <v>1.5483</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5586</v>
+        <v>1.5516</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4907</v>
+        <v>-1.4852</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0493</v>
+        <v>3.0368</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1116</v>
+        <v>3.0841</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4997</v>
+        <v>3.4773</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.553</v>
+        <v>-1.5325</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.764</v>
+        <v>0.2508</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8347</v>
+        <v>-0.0073</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0708</v>
+        <v>0.2581</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2743</v>
+        <v>0.9794</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3863</v>
+        <v>1.6408</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.112</v>
+        <v>-0.6615</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1874</v>
+        <v>-1.3736</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9609</v>
+        <v>-1.9617</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.1484</v>
+        <v>0.5881</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0324</v>
+        <v>-1.0741</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8832</v>
+        <v>-1.2001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1493</v>
+        <v>0.1259</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2198</v>
+        <v>-0.2995</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.7617</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2976</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4122</v>
+        <v>-0.0128</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9417</v>
+        <v>0.3782</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4705</v>
+        <v>-0.391</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.27</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.27</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.842</v>
+        <v>0.9696</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3064</v>
+        <v>0.7849</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4643</v>
+        <v>0.1847</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1927</v>
+        <v>0.9862</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3981</v>
+        <v>0.0116</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5909</v>
+        <v>0.9745</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6662</v>
+        <v>3.1764</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6896</v>
+        <v>0.6443</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3558</v>
+        <v>2.5321</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4735</v>
+        <v>-2.1902</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7086</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7649</v>
+        <v>-1.5576</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3564</v>
+        <v>-0.2671</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5889</v>
+        <v>-0.3836</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2326</v>
+        <v>0.1165</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.7997</v>
+        <v>2.2992</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5463</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3461</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6561</v>
+        <v>0.1003</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3166</v>
+        <v>0.1359</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6606</v>
+        <v>-0.0356</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3695</v>
+        <v>-1.2668</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9639</v>
+        <v>1.2178</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5944</v>
+        <v>-2.4846</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0506</v>
+        <v>0.092</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1917</v>
+        <v>1.4479</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1411</v>
+        <v>-1.3559</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3189</v>
+        <v>-1.3588</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7721</v>
+        <v>-0.2301</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>-1.1287</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3354</v>
+        <v>0.1103</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0212</v>
+        <v>0.2715</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3566</v>
+        <v>-0.1612</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5463</v>
+        <v>-0.1089</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7997</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2212</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1981</v>
+        <v>0.0824</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9769</v>
+        <v>-0.6202</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8512</v>
+        <v>-1.177</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1124</v>
+        <v>0.9648</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2612</v>
+        <v>-2.1418</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6972</v>
+        <v>1.028</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5452</v>
+        <v>0.8791</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.152</v>
+        <v>0.1489</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.154</v>
+        <v>-2.205</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5672</v>
+        <v>0.0857</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4132</v>
+        <v>-2.2907</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3919</v>
+        <v>1.5888</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8026</v>
+        <v>0.6478</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4107</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2667</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1032</v>
+        <v>-0.7823</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2345</v>
+        <v>1.4555</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1313</v>
+        <v>-2.2378</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9821</v>
+        <v>0.1714</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0145</v>
+        <v>1.4195</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9676</v>
+        <v>-1.2481</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1987</v>
+        <v>2.7936</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6611</v>
+        <v>2.1234</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5375</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2166</v>
+        <v>-2.6223</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.7039</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5699</v>
+        <v>-1.9184</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0415</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>-2.7316</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1384</v>
+        <v>0.3031</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9739</v>
+        <v>0.1462</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1645</v>
+        <v>0.1568</v>
       </c>
       <c r="V20" t="n">
-        <v>2.301</v>
+        <v>1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.8424</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6775</v>
+        <v>1.6269</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2444</v>
+        <v>-2.4693</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2691</v>
+        <v>1.1832</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2179</v>
+        <v>-1.4041</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4869</v>
+        <v>2.5873</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1058</v>
+        <v>2.6434</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4546</v>
+        <v>-0.7002</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3488</v>
+        <v>3.3436</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3749</v>
+        <v>-1.4603</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2368</v>
+        <v>-0.7039</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1381</v>
+        <v>-0.7563</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9046</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>0.9427</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3481</v>
+        <v>-0.2658</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1093</v>
+        <v>-1.792</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1093</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.209</v>
+        <v>-0.9064</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1346</v>
+        <v>0.1193</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3436</v>
+        <v>-1.0257</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1788</v>
+        <v>-1.8586</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4316</v>
+        <v>-2.1192</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2528</v>
+        <v>0.2607</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8119</v>
+        <v>-1.7154</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1402</v>
+        <v>-1.5588</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6717</v>
+        <v>-0.1566</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.633</v>
+        <v>-0.1432</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7086</v>
+        <v>-0.5604</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9245</v>
+        <v>0.4173</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1461</v>
+        <v>0.2693</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2087</v>
+        <v>0.7453</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0626</v>
+        <v>-0.476</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6863</v>
+        <v>-2.6061</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1479</v>
+        <v>0.898</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8342</v>
+        <v>-3.504</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9015</v>
+        <v>-1.8941</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0974</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9938</v>
+        <v>-1.9915</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3682</v>
+        <v>1.3583</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.2698</v>
+        <v>-3.2524</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5135</v>
+        <v>-2.5052</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3826</v>
+        <v>-0.3055</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2994</v>
+        <v>0.0648</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.3703</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0515</v>
+        <v>0.0488</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8252</v>
+        <v>-4.3664</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.05</v>
+        <v>-0.7101</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7751</v>
+        <v>-3.6563</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2488</v>
+        <v>-2.2444</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.5656</v>
+        <v>-3.5643</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3168</v>
+        <v>1.3199</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.424</v>
+        <v>-0.4381</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2898</v>
+        <v>-2.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8248</v>
+        <v>-1.8062</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8447</v>
+        <v>-0.3984</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2187</v>
+        <v>-0.1264</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3911</v>
+        <v>-5.4654</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5728</v>
+        <v>-2.0124</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8183</v>
+        <v>-3.453</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.7728</v>
+        <v>-3.7769</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.8772</v>
+        <v>-2.8832</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8956</v>
+        <v>-0.8937</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5857</v>
+        <v>-0.6115</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2623</v>
+        <v>-2.2795</v>
       </c>
       <c r="L25" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.187</v>
+        <v>-3.1654</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.5721</v>
+        <v>-2.5617</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6017</v>
+        <v>-0.669</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6261</v>
+        <v>-0.0351</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9757</v>
+        <v>-0.6339</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.4323</v>
+        <v>-8.1495</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.8863</v>
+        <v>-5.5673</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5461</v>
+        <v>-2.5822</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.9434</v>
+        <v>-5.9477</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.5021</v>
+        <v>-2.4989</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.4413</v>
+        <v>-3.4488</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.4687</v>
+        <v>-2.494</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.2264</v>
+        <v>-1.2345</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.2423</v>
+        <v>-1.2595</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.4747</v>
+        <v>-3.4536</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.223</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1821</v>
+        <v>0.1187</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.2153</v>
+        <v>-17.4372</v>
       </c>
       <c r="E27" t="n">
-        <v>1.361</v>
+        <v>1.075399999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.5763</v>
+        <v>-18.5126</v>
       </c>
       <c r="G27" t="n">
-        <v>-15.6315</v>
+        <v>-15.6467</v>
       </c>
       <c r="H27" t="n">
-        <v>-12.1928</v>
+        <v>-12.2055</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.4386</v>
+        <v>-3.4412</v>
       </c>
       <c r="J27" t="n">
-        <v>8.0686</v>
+        <v>7.842699999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.6055</v>
+        <v>-3.726999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>11.674</v>
+        <v>11.5695</v>
       </c>
       <c r="M27" t="n">
-        <v>-23.7</v>
+        <v>-23.4894</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.5876</v>
+        <v>-8.478400000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-15.1126</v>
+        <v>-15.0108</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.4025</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R27" t="n">
-        <v>12.4757</v>
+        <v>12.5197</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5294</v>
+        <v>1.3234</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1322</v>
+        <v>2.1568</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.6029</v>
+        <v>-0.8335000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2890999999999999</v>
+        <v>0.3005999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>7.0382</v>
+        <v>7.0101</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.7492</v>
+        <v>-6.7094</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104576_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104576_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.01</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.665</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104576_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.7094</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
